--- a/data/trans_orig/P04B3_2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101765</t>
+          <t>101860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141893</t>
+          <t>142376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74900</t>
+          <t>75118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114708</t>
+          <t>113800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188867</t>
+          <t>191058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245472</t>
+          <t>247208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84038</t>
+          <t>85027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66357</t>
+          <t>66080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100429</t>
+          <t>99799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128559</t>
+          <t>128803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175912</t>
+          <t>175644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57842</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96972</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57024</t>
+          <t>58575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89945</t>
+          <t>89817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127766</t>
+          <t>127485</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177663</t>
+          <t>179324</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>342675</t>
+          <t>343419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>396509</t>
+          <t>397496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439500</t>
+          <t>439594</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>530032</t>
+          <t>518394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>801636</t>
+          <t>800421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>902330</t>
+          <t>900209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96294</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>248966</t>
+          <t>248278</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178084</t>
+          <t>178319</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>221511</t>
+          <t>219075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>244311</t>
+          <t>250381</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445820</t>
+          <t>446940</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63751</t>
+          <t>62710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160619</t>
+          <t>159222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123189</t>
+          <t>124197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162338</t>
+          <t>161760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>173965</t>
+          <t>169106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306750</t>
+          <t>306019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102811</t>
+          <t>89697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250687</t>
+          <t>253954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149364</t>
+          <t>148189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189503</t>
+          <t>190297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240135</t>
+          <t>240063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>414915</t>
+          <t>417623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>553175</t>
+          <t>551333</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>917808</t>
+          <t>954480</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>422026</t>
+          <t>424087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>476017</t>
+          <t>477831</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1000861</t>
+          <t>1004262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1473480</t>
+          <t>1497681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67366</t>
+          <t>66877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104946</t>
+          <t>103643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>43535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120424</t>
+          <t>120875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110642</t>
+          <t>108400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206900</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81864</t>
+          <t>81225</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122499</t>
+          <t>124251</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43674</t>
+          <t>39000</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115903</t>
+          <t>115649</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>123061</t>
+          <t>124886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>219853</t>
+          <t>222339</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175770</t>
+          <t>177538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>233352</t>
+          <t>235253</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99932</t>
+          <t>91470</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252776</t>
+          <t>249198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252754</t>
+          <t>240794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>462600</t>
+          <t>459779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287211</t>
+          <t>284748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347641</t>
+          <t>347696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>454376</t>
+          <t>455963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>740624</t>
+          <t>761565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>765224</t>
+          <t>764542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1137340</t>
+          <t>1182121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173903</t>
+          <t>174554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222012</t>
+          <t>224208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>251693</t>
+          <t>250390</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>495545</t>
+          <t>470190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>445342</t>
+          <t>442527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>699208</t>
+          <t>701269</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129760</t>
+          <t>128684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177547</t>
+          <t>175249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124585</t>
+          <t>123517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178027</t>
+          <t>178579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273428</t>
+          <t>268534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345755</t>
+          <t>343850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>138570</t>
+          <t>137417</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>184417</t>
+          <t>185246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142998</t>
+          <t>145867</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>207620</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>303404</t>
+          <t>299341</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378150</t>
+          <t>378736</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>383260</t>
+          <t>380490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>449045</t>
+          <t>449635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>348201</t>
+          <t>357034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>480729</t>
+          <t>484192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>767325</t>
+          <t>761178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>911786</t>
+          <t>911203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>465601</t>
+          <t>446506</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>657962</t>
+          <t>654071</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>592220</t>
+          <t>598131</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>866976</t>
+          <t>878198</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1136772</t>
+          <t>1141418</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1481489</t>
+          <t>1479373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>352507</t>
+          <t>345707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>492777</t>
+          <t>492840</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>377338</t>
+          <t>375100</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512781</t>
+          <t>511177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,47 +3169,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>906202</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>781012</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>990492</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>13,82%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>906202</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>786088</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>985818</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>484051</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>699783</t>
+          <t>698913</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>493712</t>
+          <t>490102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>675052</t>
+          <t>673658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1085969</t>
+          <t>1064088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1350896</t>
+          <t>1345885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1645153</t>
+          <t>1651354</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2142814</t>
+          <t>2185610</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1786584</t>
+          <t>1789669</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2244576</t>
+          <t>2263394</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3501702</t>
+          <t>3475101</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4196237</t>
+          <t>4185219</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>121073</t>
+          <t>135497</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101860</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142376</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>98320</t>
+          <t>109947</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75118</t>
+          <t>94405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113800</t>
+          <t>128406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>219393</t>
+          <t>245444</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191058</t>
+          <t>220223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247208</t>
+          <t>276465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68966</t>
+          <t>75511</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53853</t>
+          <t>60261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85027</t>
+          <t>92129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84713</t>
+          <t>97035</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66080</t>
+          <t>83210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99799</t>
+          <t>112437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>153679</t>
+          <t>172546</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128803</t>
+          <t>151831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175644</t>
+          <t>195760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75027</t>
+          <t>82547</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58539</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94880</t>
+          <t>103706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>84960</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89817</t>
+          <t>100253</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>149902</t>
+          <t>167507</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127485</t>
+          <t>146356</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179324</t>
+          <t>193351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>370374</t>
+          <t>397155</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>343419</t>
+          <t>369657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>397496</t>
+          <t>425497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>467423</t>
+          <t>442238</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439594</t>
+          <t>420138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>518394</t>
+          <t>463771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>837798</t>
+          <t>839392</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>800421</t>
+          <t>804539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>900209</t>
+          <t>876737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>188123</t>
+          <t>223973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85213</t>
+          <t>197029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>248278</t>
+          <t>253201</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>196938</t>
+          <t>227035</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178319</t>
+          <t>203601</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>219075</t>
+          <t>252013</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>385062</t>
+          <t>451008</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>250381</t>
+          <t>417871</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>446940</t>
+          <t>488474</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>119409</t>
+          <t>135461</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62710</t>
+          <t>114599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159222</t>
+          <t>160364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>141506</t>
+          <t>157264</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124197</t>
+          <t>137424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161760</t>
+          <t>179310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>260916</t>
+          <t>292726</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169106</t>
+          <t>262298</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306019</t>
+          <t>327642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>189660</t>
+          <t>203345</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89697</t>
+          <t>173081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253954</t>
+          <t>233687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>168788</t>
+          <t>189358</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148189</t>
+          <t>168562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>190297</t>
+          <t>211524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>358448</t>
+          <t>392703</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240063</t>
+          <t>353966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>417623</t>
+          <t>431162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>695671</t>
+          <t>486138</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>551333</t>
+          <t>449308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>954480</t>
+          <t>525076</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>449831</t>
+          <t>494758</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>424087</t>
+          <t>465568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>477831</t>
+          <t>525182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1145503</t>
+          <t>980896</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1004262</t>
+          <t>934229</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1497681</t>
+          <t>1028202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957064</t>
+          <t>1068416</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957064</t>
+          <t>1068416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957064</t>
+          <t>1068416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2149928</t>
+          <t>2117333</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2149928</t>
+          <t>2117333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2149928</t>
+          <t>2117333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>83820</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66877</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103643</t>
+          <t>115367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88024</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>84230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120875</t>
+          <t>118430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>171844</t>
+          <t>194621</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108400</t>
+          <t>170547</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208802</t>
+          <t>224091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100299</t>
+          <t>112464</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>91545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124251</t>
+          <t>135354</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83371</t>
+          <t>104721</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115649</t>
+          <t>124729</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>183670</t>
+          <t>217185</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>124886</t>
+          <t>191568</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>222339</t>
+          <t>247323</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>203555</t>
+          <t>229221</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>177538</t>
+          <t>199556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>235253</t>
+          <t>256915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>185856</t>
+          <t>224094</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91470</t>
+          <t>201947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249198</t>
+          <t>248362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>389411</t>
+          <t>453315</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240794</t>
+          <t>418294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459779</t>
+          <t>493533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>316841</t>
+          <t>366129</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>284748</t>
+          <t>336743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347696</t>
+          <t>400889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>575460</t>
+          <t>382197</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>455963</t>
+          <t>356319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>761565</t>
+          <t>409907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>892301</t>
+          <t>748326</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>764542</t>
+          <t>705227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1182121</t>
+          <t>786795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932710</t>
+          <t>811552</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1637226</t>
+          <t>1613447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>198991</t>
+          <t>236167</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>174554</t>
+          <t>209197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224208</t>
+          <t>264476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>312285</t>
+          <t>289463</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250390</t>
+          <t>263752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>470190</t>
+          <t>317550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>511276</t>
+          <t>525630</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>442527</t>
+          <t>488765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>701269</t>
+          <t>563782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>151413</t>
+          <t>165816</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128684</t>
+          <t>141055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175249</t>
+          <t>193739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>156524</t>
+          <t>170844</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123517</t>
+          <t>150302</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>178579</t>
+          <t>191821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>307937</t>
+          <t>336660</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268534</t>
+          <t>304417</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343850</t>
+          <t>369234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>159919</t>
+          <t>167548</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>137417</t>
+          <t>143792</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>185246</t>
+          <t>194368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>182903</t>
+          <t>197000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145867</t>
+          <t>176360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>207620</t>
+          <t>221124</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>342823</t>
+          <t>364548</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>299341</t>
+          <t>330101</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378736</t>
+          <t>397347</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>416343</t>
+          <t>418888</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>380490</t>
+          <t>385583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>449635</t>
+          <t>452749</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>442331</t>
+          <t>460012</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>357034</t>
+          <t>430657</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>484192</t>
+          <t>488642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>858674</t>
+          <t>878900</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>761178</t>
+          <t>837260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>911203</t>
+          <t>923960</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926666</t>
+          <t>988419</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926666</t>
+          <t>988419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926666</t>
+          <t>988419</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094043</t>
+          <t>1117320</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094043</t>
+          <t>1117320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094043</t>
+          <t>1117320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2020710</t>
+          <t>2105739</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2020710</t>
+          <t>2105739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2020710</t>
+          <t>2105739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>592007</t>
+          <t>689718</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>446506</t>
+          <t>641930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>654071</t>
+          <t>741806</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>695567</t>
+          <t>726985</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>598131</t>
+          <t>688236</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>878198</t>
+          <t>773570</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1287574</t>
+          <t>1416703</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1141418</t>
+          <t>1354131</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1479373</t>
+          <t>1485203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>440088</t>
+          <t>489252</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>345707</t>
+          <t>444064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>492840</t>
+          <t>530529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>466114</t>
+          <t>529865</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>375100</t>
+          <t>492351</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>511177</t>
+          <t>567830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>906202</t>
+          <t>1019117</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>781012</t>
+          <t>962535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>990492</t>
+          <t>1077239</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>628162</t>
+          <t>682661</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>484051</t>
+          <t>629727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>698913</t>
+          <t>737750</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>612421</t>
+          <t>695413</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>490102</t>
+          <t>653627</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>673658</t>
+          <t>736934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1240583</t>
+          <t>1378074</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1064088</t>
+          <t>1314409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1345885</t>
+          <t>1448793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1799231</t>
+          <t>1668310</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1651354</t>
+          <t>1604490</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2185610</t>
+          <t>1740686</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1935045</t>
+          <t>1779205</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1789669</t>
+          <t>1721265</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2263394</t>
+          <t>1830214</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3734276</t>
+          <t>3447514</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3475101</t>
+          <t>3371320</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4185219</t>
+          <t>3530460</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
